--- a/htr-Corps-ModeleMetier/ig/mappingPersonneStructureAuteurFHIR.xlsx
+++ b/htr-Corps-ModeleMetier/ig/mappingPersonneStructureAuteurFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-27T08:14:05+00:00</t>
+    <t>2025-05-27T14:36:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Corps-ModeleMetier/ig/mappingPersonneStructureAuteurFHIR.xlsx
+++ b/htr-Corps-ModeleMetier/ig/mappingPersonneStructureAuteurFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-27T14:36:02+00:00</t>
+    <t>2025-06-05T15:38:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Corps-ModeleMetier/ig/mappingPersonneStructureAuteurFHIR.xlsx
+++ b/htr-Corps-ModeleMetier/ig/mappingPersonneStructureAuteurFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-05T15:38:56+00:00</t>
+    <t>2025-10-06T12:29:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Corps-ModeleMetier/ig/mappingPersonneStructureAuteurFHIR.xlsx
+++ b/htr-Corps-ModeleMetier/ig/mappingPersonneStructureAuteurFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-06T12:29:55+00:00</t>
+    <t>2025-10-13T08:32:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Corps-ModeleMetier/ig/mappingPersonneStructureAuteurFHIR.xlsx
+++ b/htr-Corps-ModeleMetier/ig/mappingPersonneStructureAuteurFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T08:32:48+00:00</t>
+    <t>2025-10-21T08:19:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Corps-ModeleMetier/ig/mappingPersonneStructureAuteurFHIR.xlsx
+++ b/htr-Corps-ModeleMetier/ig/mappingPersonneStructureAuteurFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T08:19:27+00:00</t>
+    <t>2025-10-21T12:36:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
